--- a/web/files/九龙-红磡-悦麓.xlsx
+++ b/web/files/九龙-红磡-悦麓.xlsx
@@ -1061,7 +1061,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3720,23 +3720,19 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>6136000</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>23068</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3745,12 +3741,12 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -3760,7 +3756,7 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3790,23 +3786,19 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>6100500</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>23108</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3815,12 +3807,12 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -3830,7 +3822,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3857,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -4001,7 +3993,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4067,7 +4059,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4133,7 +4125,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4199,7 +4191,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4265,7 +4257,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4331,7 +4323,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4397,7 +4389,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4463,7 +4455,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4529,7 +4521,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4595,7 +4587,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4661,7 +4653,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4727,7 +4719,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4793,7 +4785,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4859,7 +4851,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4925,7 +4917,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4991,7 +4983,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -5057,7 +5049,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -5123,7 +5115,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5189,7 +5181,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5255,7 +5247,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5387,7 +5379,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5453,7 +5445,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5651,7 +5643,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5717,7 +5709,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5783,7 +5775,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5849,7 +5841,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5915,7 +5907,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -6051,7 +6043,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -6117,7 +6109,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6249,7 +6241,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6357,7 +6349,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -6367,7 +6359,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6464,7 +6456,7 @@
           <t>A | 288呎 (1房)
 $724万
 $25,147/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -6472,7 +6464,7 @@
           <t>B | 267呎 (1房)
 $666万
 $24,950/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -6480,7 +6472,7 @@
           <t>C | 266呎 (1房)
 $650万
 $24,451/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -6488,7 +6480,7 @@
           <t>D | 252呎 (1房)
 $597万
 $23,703/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr"/>
@@ -6504,7 +6496,7 @@
           <t>A | 288呎 (1房)
 $660万
 $22,901/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -6512,7 +6504,7 @@
           <t>B | 267呎 (1房)
 $665万
 $24,913/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -6520,7 +6512,7 @@
           <t>C | 266呎 (1房)
 $605万
 $22,736/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -6528,7 +6520,7 @@
           <t>D | 252呎 (1房)
 $568万
 $22,541/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr"/>
@@ -6544,7 +6536,7 @@
           <t>A | 288呎 (1房)
 $656万
 $22,787/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -6560,7 +6552,7 @@
           <t>C | 266呎 (1房)
 $615万
 $23,137/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -6568,7 +6560,7 @@
           <t>D | 252呎 (1房)
 $565万
 $22,429/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr"/>
@@ -6624,7 +6616,7 @@
           <t>A | 288呎 (1房)
 $614万
 $21,334/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -6632,7 +6624,7 @@
           <t>B | 267呎 (1房)
 $590万
 $22,104/呎
-(26年-02月-19日)</t>
+(26年-02月-20日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -6640,7 +6632,7 @@
           <t>C | 266呎 (1房)
 $609万
 $22,907/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -6648,7 +6640,7 @@
           <t>D | 252呎 (1房)
 $560万
 $22,206/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -6672,7 +6664,7 @@
           <t>B | 265呎 (1房)
 $603万
 $22,742/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -6680,7 +6672,7 @@
           <t>C | 266呎 (1房)
 $606万
 $22,794/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -6688,7 +6680,7 @@
           <t>D | 252呎 (1房)
 $557万
 $22,096/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>
@@ -6704,7 +6696,7 @@
           <t>A | 189呎 (开放式)
 $388万
 $20,504/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -6712,7 +6704,7 @@
           <t>B | 196呎 (开放式)
 $358万
 $18,286/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -6720,7 +6712,7 @@
           <t>C | 248呎 (1房)
 $560万
 $22,576/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -6728,7 +6720,7 @@
           <t>D | 267呎 (1房)
 $591万
 $22,125/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -6736,7 +6728,7 @@
           <t>E | 252呎 (1房)
 $540万
 $21,447/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6743,7 @@
           <t>A | 189呎 (开放式)
 $367万
 $19,417/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -6759,7 +6751,7 @@
           <t>B | 196呎 (开放式)
 $353万
 $18,017/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -6767,7 +6759,7 @@
           <t>C | 248呎 (1房)
 $552万
 $22,242/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -6775,7 +6767,7 @@
           <t>D | 267呎 (1房)
 $582万
 $21,798/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -6783,7 +6775,7 @@
           <t>E | 252呎 (1房)
 $532万
 $21,131/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6806,7 @@
           <t>C | 248呎 (1房)
 $514万
 $20,723/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -6822,7 +6814,7 @@
           <t>D | 267呎 (1房)
 $530万
 $19,857/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -6830,7 +6822,7 @@
           <t>E | 252呎 (1房)
 $485万
 $19,249/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
     </row>
@@ -6853,23 +6845,23 @@
           <t>B | 283呎 (1房)
 $577万
 $20,390/呎
-(26年-02月-19日)</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
+(26年-02月-20日)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 264呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
+$610万
+$23,108/呎
+(26年-07月-27日)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (1房)
-招标单位
--
-(在售)</t>
+$614万
+$23,068/呎
+(26年-07月-27日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -6877,7 +6869,7 @@
           <t>E | 268呎 (1房)
 $590万
 $22,030/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6884,7 @@
           <t>A | 201呎 (开放式)
 $373万
 $18,569/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -6900,7 +6892,7 @@
           <t>B | 283呎 (1房)
 $602万
 $21,271/呎
-(26年-02月-19日)</t>
+(26年-02月-20日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -6908,7 +6900,7 @@
           <t>C | 264呎 (1房)
 $562万
 $21,271/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -6916,7 +6908,7 @@
           <t>D | 266呎 (1房)
 $554万
 $20,845/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -6924,7 +6916,7 @@
           <t>E | 268呎 (1房)
 $542万
 $20,207/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -6939,7 +6931,7 @@
           <t>A | 203呎 (开放式)
 $355万
 $17,493/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -6947,7 +6939,7 @@
           <t>B | 283呎 (1房)
 $548万
 $19,377/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -6955,7 +6947,7 @@
           <t>C | 282呎 (1房)
 $546万
 $19,377/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -6963,7 +6955,7 @@
           <t>D | 267呎 (1房)
 $507万
 $18,990/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -6971,7 +6963,7 @@
           <t>E | 304呎 (1房)
 $579万
 $19,036/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6978,7 @@
           <t>A | 203呎 (开放式)
 $346万
 $17,045/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -6994,7 +6986,7 @@
           <t>B | 283呎 (1房)
 $540万
 $19,090/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -7002,7 +6994,7 @@
           <t>C | 282呎 (1房)
 $538万
 $19,091/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -7010,7 +7002,7 @@
           <t>D | 267呎 (1房)
 $500万
 $18,709/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -7018,7 +7010,7 @@
           <t>E | 304呎 (1房)
 $564万
 $18,548/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7025,7 @@
           <t>A | 203呎 (开放式)
 $340万
 $16,739/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -7041,7 +7033,7 @@
           <t>B | 283呎 (1房)
 $532万
 $18,808/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -7049,7 +7041,7 @@
           <t>C | 282呎 (1房)
 $530万
 $18,809/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -7057,7 +7049,7 @@
           <t>D | 267呎 (1房)
 $492万
 $18,433/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -7065,7 +7057,7 @@
           <t>E | 304呎 (1房)
 $589万
 $19,371/呎
-(26年-03月-15日)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7088,7 @@
           <t>C | 282呎 (1房)
 $621万
 $22,008/呎
-(26年-07月-17日)</t>
+(26年-07月-18日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -7104,7 +7096,7 @@
           <t>D | 267呎 (1房)
 $586万
 $21,936/呎
-(26年-07月-21日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -7127,7 +7119,7 @@
           <t>A | 203呎 (开放式)
 $325万
 $15,988/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -7135,7 +7127,7 @@
           <t>B | 283呎 (1房)
 $521万
 $18,396/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -7143,7 +7135,7 @@
           <t>C | 282呎 (1房)
 $519万
 $18,396/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -7151,7 +7143,7 @@
           <t>D | 267呎 (1房)
 $481万
 $18,028/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -7159,7 +7151,7 @@
           <t>E | 304呎 (1房)
 $531万
 $17,476/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7166,7 @@
           <t>A | 166呎 (开放式)
 $426万
 $25,688/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -7190,7 +7182,7 @@
           <t>C | 244呎 (1房)
 $572万
 $23,425/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -7198,7 +7190,7 @@
           <t>D | 229呎 (1房)
 $553万
 $24,130/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">

--- a/web/files/九龙-红磡-悦麓.xlsx
+++ b/web/files/九龙-红磡-悦麓.xlsx
@@ -1716,12 +1716,12 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6539,12 +6539,12 @@
 (26年-02月-16日)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 267呎 (1房)
 $683万
 $25,588/呎
-(在售)</t>
+(26年-07月-31日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">

--- a/web/files/九龙-红磡-悦麓.xlsx
+++ b/web/files/九龙-红磡-悦麓.xlsx
@@ -1848,23 +1848,19 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>6410300</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>25438</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1873,12 +1869,12 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -1888,7 +1884,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5441,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -6349,7 +6345,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -6359,7 +6355,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6595,12 +6591,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 252呎 (1房)
-招标单位
--
-(在售)</t>
+$641万
+$25,438/呎
+(26年-08月-08日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr"/>
@@ -7088,7 +7084,7 @@
           <t>C | 282呎 (1房)
 $621万
 $22,008/呎
-(26年-07月-18日)</t>
+(26年-08月-10日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">

--- a/web/files/九龙-红磡-悦麓.xlsx
+++ b/web/files/九龙-红磡-悦麓.xlsx
@@ -5375,7 +5375,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -7092,7 +7092,7 @@
           <t>D | 267呎 (1房)
 $586万
 $21,936/呎
-(26年-07月-22日)</t>
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">

--- a/web/files/九龙-红磡-悦麓.xlsx
+++ b/web/files/九龙-红磡-悦麓.xlsx
@@ -3721,7 +3721,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -6849,7 +6849,7 @@
           <t>C | 264呎 (1房)
 $610万
 $23,108/呎
-(26年-07月-27日)</t>
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -6857,7 +6857,7 @@
           <t>D | 266呎 (1房)
 $614万
 $23,068/呎
-(26年-07月-27日)</t>
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">

--- a/web/files/九龙-红磡-悦麓.xlsx
+++ b/web/files/九龙-红磡-悦麓.xlsx
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -6540,7 +6540,7 @@
           <t>B | 267呎 (1房)
 $683万
 $25,588/呎
-(26年-07月-31日)</t>
+(26年-08月-19日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">

--- a/web/files/九龙-红磡-悦麓.xlsx
+++ b/web/files/九龙-红磡-悦麓.xlsx
@@ -1853,7 +1853,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -6596,7 +6596,7 @@
           <t>D | 252呎 (1房)
 $641万
 $25,438/呎
-(26年-08月-08日)</t>
+(26年-08月-27日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr"/>
